--- a/AAII_Financials/Quarterly/DOW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DOW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>DOW</t>
   </si>
@@ -656,480 +656,493 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>12092000</v>
+      </c>
+      <c r="E8" s="3">
         <v>9794000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9460000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9973000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>10104000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>10431000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>10405000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10879000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>10915000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>10765000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10621000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10730000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11420000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>11851000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11859000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>14115000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>15664000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>15264000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>14364000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>14837000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>13885000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>11882000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>10706000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>9712000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8354000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>9770000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>10204000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>10764000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>11014000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>10969000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>11944000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>12634000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>12789000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>12237000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3033000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>9925000</v>
+      </c>
+      <c r="E9" s="3">
         <v>9154000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8912000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9242000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>9521000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>9760000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>9395000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>9809000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9591000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>9488000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>9646000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>9592000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>9875000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10452000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10656000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>12381000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>12899000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>12402000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>11778000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>11611000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>10740000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>10062000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>9132000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>8359000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>7604000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8234000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>8718000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>9377000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>9420000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>9138000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>21918000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>10456000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>10540000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>9980000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>16726000</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2167000</v>
+      </c>
+      <c r="E10" s="3">
         <v>640000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>548000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>731000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>583000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>671000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1010000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1070000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1324000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1277000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>975000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1138000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1545000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1399000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1203000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1734000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2765000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2862000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2586000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3226000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3145000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1820000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1574000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1353000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>750000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1536000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1486000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1387000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1594000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1831000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>-9974000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2178000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2249000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2257000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>-13693000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1167,115 +1180,119 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>207000</v>
+      </c>
+      <c r="E12" s="3">
         <v>181000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>173000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>191000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>188000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>200000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>202000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>208000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>196000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>204000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>213000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>197000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>205000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>214000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>225000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>191000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>217000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>218000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>225000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>210000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>228000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>194000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>214000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>193000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>182000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>179000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>173000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>194000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>208000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>190000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>178000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>193000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>221000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>208000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>413000</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1381,120 +1398,126 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>440000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-19000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>991000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-71000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>507000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>271000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>66000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-4000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-16000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>36000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>479000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-21000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>12000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>662000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-135000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>7000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>8000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>174000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-51000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>418000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>129000</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>54000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>680000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>52000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>161000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>2950000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>311000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>413000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>608000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>426000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>361000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>302000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>311000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>2883000</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>46000</v>
+        <v>40000</v>
       </c>
       <c r="E15" s="3">
         <v>46000</v>
@@ -1503,10 +1526,10 @@
         <v>46000</v>
       </c>
       <c r="G15" s="3">
+        <v>46000</v>
+      </c>
+      <c r="H15" s="3">
         <v>63000</v>
-      </c>
-      <c r="H15" s="3">
-        <v>76000</v>
       </c>
       <c r="I15" s="3">
         <v>76000</v>
@@ -1515,10 +1538,10 @@
         <v>76000</v>
       </c>
       <c r="K15" s="3">
+        <v>76000</v>
+      </c>
+      <c r="L15" s="3">
         <v>77000</v>
-      </c>
-      <c r="L15" s="3">
-        <v>81000</v>
       </c>
       <c r="M15" s="3">
         <v>81000</v>
@@ -1533,34 +1556,34 @@
         <v>81000</v>
       </c>
       <c r="Q15" s="3">
+        <v>81000</v>
+      </c>
+      <c r="R15" s="3">
         <v>80000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>83000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>85000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>88000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>87000</v>
-      </c>
-      <c r="V15" s="3">
-        <v>100000</v>
       </c>
       <c r="W15" s="3">
         <v>100000</v>
       </c>
       <c r="X15" s="3">
-        <v>101000</v>
+        <v>100000</v>
       </c>
       <c r="Y15" s="3">
         <v>101000</v>
       </c>
       <c r="Z15" s="3">
-        <v>100000</v>
+        <v>101000</v>
       </c>
       <c r="AA15" s="3">
         <v>100000</v>
@@ -1569,34 +1592,37 @@
         <v>100000</v>
       </c>
       <c r="AC15" s="3">
+        <v>100000</v>
+      </c>
+      <c r="AD15" s="3">
         <v>99000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>100000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>104000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>116000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>269000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>272000</v>
-      </c>
-      <c r="AI15" s="3">
-        <v>118000</v>
       </c>
       <c r="AJ15" s="3">
         <v>118000</v>
       </c>
       <c r="AK15" s="3">
+        <v>118000</v>
+      </c>
+      <c r="AL15" s="3">
         <v>157000</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1631,222 +1657,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>10690000</v>
+      </c>
+      <c r="E17" s="3">
         <v>9793000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9757000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9783000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>10083000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>10364000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9945000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>10428000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10193000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10154000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10279000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10153000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10472000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11079000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11212000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>13018000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>13652000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>13380000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>12459000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>12742000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>11637000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>10723000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>9909000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9704000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8295000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>9008000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>12272000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>10370000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>10567000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>10500000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>11224000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>11536000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>11666000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>11099000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>6708000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1402000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-297000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>190000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>21000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>67000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>460000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>451000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>722000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>611000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>342000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>577000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>948000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>772000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>647000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1097000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2012000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1884000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1905000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2095000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2248000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1159000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>797000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>8000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>59000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>762000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2068000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>394000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>447000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>469000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>720000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1098000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1123000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1138000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-3675000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1884,543 +1917,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-81000</v>
+      </c>
+      <c r="E20" s="3">
         <v>233000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>79000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>17000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-18000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>16000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-32000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-25000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-8000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>61000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>33000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>119000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>121000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>393000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>59000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>322000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>338000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>383000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>331000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>395000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>360000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1267000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>232000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-43000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-133000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>94000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>276000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>5000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>69000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>107000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>154000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>197000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>275000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-246000</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1523000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-186000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-330000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>219000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>81000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>161000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>520000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>559000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>824000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>700000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>362000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>625000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>910000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>732000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1694000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1824000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3018000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2974000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2943000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3151000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>3388000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2236000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2790000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>964000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>716000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1353000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-1261000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1409000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1195000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1281000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1553000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1984000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1934000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>2250000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-3693000</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>219000</v>
+        <v>210000</v>
       </c>
       <c r="E22" s="3">
         <v>219000</v>
       </c>
       <c r="F22" s="3">
+        <v>219000</v>
+      </c>
+      <c r="G22" s="3">
         <v>221000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>209000</v>
-      </c>
-      <c r="H22" s="3">
-        <v>216000</v>
       </c>
       <c r="I22" s="3">
         <v>216000</v>
       </c>
       <c r="J22" s="3">
+        <v>216000</v>
+      </c>
+      <c r="K22" s="3">
         <v>199000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>197000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>199000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>197000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>192000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>172000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>185000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>175000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>155000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>165000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>167000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>170000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>178000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>187000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>196000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>248000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>198000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>199000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>233000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>222000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>233000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>237000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>241000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>282000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>258000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>261000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>262000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>213000</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>871000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-390000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1548000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>70000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-659000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-374000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>219000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>324000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>608000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>449000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-352000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>417000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>711000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-120000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>865000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1001000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2169000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2055000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2118000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2248000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2456000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1323000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1816000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>42000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-183000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>396000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2196000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>437000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>215000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>297000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>545000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>994000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1059000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1151000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-4134000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E24" s="3">
         <v>55000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-71000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-54000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>142000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-84000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>254000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>84000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>150000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-89000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-257000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>90000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>210000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-47000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>218000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>241000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>488000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>503000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>357000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>542000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>524000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>317000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>562000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>43000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>34000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>138000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>114000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>90000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>125000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>141000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>54000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>280000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>249000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>226000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>232000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2526,222 +2575,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>802000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-445000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1477000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>124000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-801000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-290000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-35000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>240000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>458000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>538000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-95000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>327000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>501000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-73000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>647000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>760000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1681000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1552000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1761000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1706000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1932000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1006000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1254000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-217000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>258000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2310000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>347000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>90000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>156000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>491000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>714000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>810000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>925000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-4366000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>-535000</v>
+        <v>715000</v>
       </c>
       <c r="E27" s="3">
+        <v>-531000</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1545000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>60000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-839000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-310000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-56000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>211000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>436000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>513000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-108000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>300000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>482000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-96000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>610000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>735000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1652000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1561000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1727000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1675000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1891000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>986000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1234000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-28000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-227000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>237000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2323000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>333000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>75000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>111000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>459000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>678000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>779000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>890000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-4409000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2847,8 +2905,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2937,25 +2998,28 @@
         <v>0</v>
       </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>445000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>432000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>335000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>554000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>514000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>1882000</v>
       </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3061,8 +3125,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3168,222 +3235,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>81000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-233000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-79000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-17000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>18000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-16000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>32000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>25000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>8000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-61000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-33000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-119000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-121000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-393000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-59000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-322000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-338000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-383000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-331000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-395000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-360000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1267000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-232000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>43000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>133000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-94000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-276000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-69000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-107000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-154000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-197000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-275000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>246000</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>721000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-533000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1543000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>62000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-835000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-307000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-53000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>214000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>439000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>516000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-105000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>302000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>485000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-93000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>610000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>735000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1652000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1561000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1727000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1675000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1891000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>986000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1234000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-28000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-227000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>237000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2323000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>333000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>75000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>556000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>891000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1013000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1333000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1404000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-2527000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3489,227 +3565,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>721000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-533000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1543000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>62000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-835000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-307000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-53000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>214000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>439000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>516000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-105000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>302000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>485000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-93000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>610000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>735000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1652000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1561000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1727000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1675000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1891000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>986000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1234000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-28000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-227000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>237000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2323000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>333000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>75000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>556000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>891000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1013000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1333000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1404000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-2527000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -3747,8 +3832,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3786,160 +3872,164 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>3736000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3851000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3816000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4609000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2399000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1465000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2189000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2883000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3341000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3723000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2987000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3080000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2924000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3319000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3886000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2216000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2367000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3143000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2988000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2911000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3491000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4133000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5104000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4549000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3724000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3633000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2367000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2823000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2446000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2969000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2724000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3403000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4823000</v>
-      </c>
-      <c r="AJ41" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="AK41" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AL41" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>500000</v>
+      </c>
+      <c r="E42" s="3">
         <v>479000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>454000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>539000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>339000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>9000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>383000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>400000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>570000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>771000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1301000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>914000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>717000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>621000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -3964,793 +4054,817 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-      <c r="Z42" s="3" t="s">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>21000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>11000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>20000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>101000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>100000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>176000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>203000</v>
-      </c>
-      <c r="AJ42" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="AK42" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AL42" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8148000</v>
+      </c>
+      <c r="E43" s="3">
         <v>7078000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6638000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7161000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7654000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7184000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6864000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7317000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7079000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7082000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6627000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7411000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7673000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7833000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7803000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>8570000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>9753000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>10059000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>9633000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>9461000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>9157000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>8347000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>7452000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>7089000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>6887000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>7633000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>7596000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>8886000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>8603000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>12401000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>9054000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>12961000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>13106000</v>
-      </c>
-      <c r="AJ43" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="AK43" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AL43" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7233000</v>
+      </c>
+      <c r="E44" s="3">
         <v>6775000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6595000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6675000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>6701000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6765000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6544000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6741000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6459000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6373000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6076000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6211000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>6487000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>6825000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>6988000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>7571000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>8225000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>7760000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>7372000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>7111000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>6952000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>6157000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5701000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5609000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5784000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>6324000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>6214000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>6416000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>6841000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>9508000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>16159000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>9615000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>9346000</v>
-      </c>
-      <c r="AJ44" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="AK44" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AL44" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>886000</v>
+      </c>
+      <c r="E45" s="3">
         <v>902000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>423000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>517000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>502000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>815000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>536000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>532000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>560000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>469000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>562000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>682000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>689000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>647000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1800000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1420000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1424000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1203000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>855000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>910000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>752000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>526000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>827000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>542000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>600000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>547000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>617000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>813000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>727000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>682000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>21445000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>805000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>808000</v>
-      </c>
-      <c r="AJ45" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="AK45" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AL45" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>20871000</v>
+      </c>
+      <c r="E46" s="3">
         <v>19469000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18062000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>19646000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>17712000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16328000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16590000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>17977000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>18053000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>18448000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>17614000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>18298000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>18549000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>19356000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>20477000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>19777000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>21769000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>22165000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>20848000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>20393000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>20352000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>19163000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>19084000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>17789000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>16997000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>18138000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>16815000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>18949000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>18637000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>25661000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>39370000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>26960000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>28286000</v>
-      </c>
-      <c r="AJ46" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="AK46" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AL46" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4973000</v>
+      </c>
+      <c r="E47" s="3">
         <v>4590000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4591000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4499000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4488000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4511000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4679000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4682000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4544000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4453000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4448000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4748000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4719000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4952000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>5064000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>5035000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>5206000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>5366000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>5742000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>5474000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>5026000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4538000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4578000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>4246000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>4207000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>4085000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>5059000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>6628000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>6313000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>6450000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>6327000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>6959000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>6782000</v>
-      </c>
-      <c r="AJ47" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="AK47" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AL47" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>23575000</v>
+      </c>
+      <c r="E48" s="3">
         <v>23534000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>23606000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>23853000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>23722000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>23650000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>23272000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>23394000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>22911000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>22625000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>22386000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>21848000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>21699000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21580000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>21669000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>21263000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>21432000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>21686000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>21967000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>21375000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>21609000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>21707000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>22095000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>22222000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>22499000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>22748000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>23068000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>23133000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>23433000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>26076000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>21418000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>23396000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>23392000</v>
-      </c>
-      <c r="AJ48" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="AK48" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AL48" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9305000</v>
+      </c>
+      <c r="E49" s="3">
         <v>9373000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9464000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10236000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10304000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10271000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10286000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10524000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10434000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10557000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10713000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10712000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10846000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10989000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>11086000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>11007000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>11221000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>11477000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>11645000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>11763000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>11926000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>12018000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>12260000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>12296000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>12333000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>12416000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>12555000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>13644000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>13848000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>18555000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>18984000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>18925000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>19130000</v>
-      </c>
-      <c r="AJ49" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="AK49" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AL49" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4856,8 +4970,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4963,8 +5080,11 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4972,106 +5092,109 @@
         <v>10000</v>
       </c>
       <c r="E52" s="3">
+        <v>10000</v>
+      </c>
+      <c r="F52" s="3">
         <v>8000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>14000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>19000</v>
-      </c>
-      <c r="K52" s="3">
-        <v>5000</v>
       </c>
       <c r="L52" s="3">
         <v>5000</v>
       </c>
       <c r="M52" s="3">
+        <v>5000</v>
+      </c>
+      <c r="N52" s="3">
         <v>895000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3000</v>
       </c>
-      <c r="P52" s="3" t="s">
+      <c r="Q52" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2307000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2475000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2515000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2641000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2788000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2744000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2855000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3011000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3453000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3392000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3240000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3299000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3027000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2583000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2658000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2995000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>3309000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2811000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2631000</v>
-      </c>
-      <c r="AJ52" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="AK52" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AL52" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5177,115 +5300,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>61585000</v>
+      </c>
+      <c r="E54" s="3">
         <v>59780000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>58538000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>60990000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>58991000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>57499000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>57312000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>59389000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>58526000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>58817000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>57967000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>58288000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>58294000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>59316000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>60603000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>59557000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>62143000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>63335000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>62990000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>61749000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>61768000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>60437000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>61470000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>59945000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>59276000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>60686000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>60524000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>64937000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>64889000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>79737000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>83699000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>79051000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>80221000</v>
-      </c>
-      <c r="AJ54" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="AK54" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AL54" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5323,8 +5452,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5362,650 +5492,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7007000</v>
+      </c>
+      <c r="E57" s="3">
         <v>6161000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5545000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6208000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6641000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6616000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6541000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7048000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6969000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6787000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6326000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6318000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6165000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6560000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4940000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5008000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5693000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5769000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5577000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4601000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4664000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4200000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3763000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3400000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3296000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3769000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3889000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3855000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>4188000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>5103000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>4456000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>5549000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>5224000</v>
-      </c>
-      <c r="AJ57" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="AK57" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AL57" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1193000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1235000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>656000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>870000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>877000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>968000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>977000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>723000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>744000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>573000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>530000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>702000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>527000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>829000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>724000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>549000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>656000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>447000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>392000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>561000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>648000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>644000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>616000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>676000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1304000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1874000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1021000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>895000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>841000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2686000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>636000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3515000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3699000</v>
-      </c>
-      <c r="AJ58" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="AK58" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AL58" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1129000</v>
+      </c>
+      <c r="E59" s="3">
         <v>869000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>792000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>767000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>928000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>742000</v>
-      </c>
-      <c r="I59" s="3">
-        <v>660000</v>
       </c>
       <c r="J59" s="3">
         <v>660000</v>
       </c>
       <c r="K59" s="3">
+        <v>660000</v>
+      </c>
+      <c r="L59" s="3">
         <v>598000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>755000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>758000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1103000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1029000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1168000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5667000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6758000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6960000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6838000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>7257000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7631000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6996000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>6510000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>6729000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>6131000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>5186000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>5478000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>5769000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>6451000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>6576000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>7584000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>14066000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>7762000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>7969000</v>
-      </c>
-      <c r="AJ59" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="AK59" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AL59" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11931000</v>
+      </c>
+      <c r="E60" s="3">
         <v>10536000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9183000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10104000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10486000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10586000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10288000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10827000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10308000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10249000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9957000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10248000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9649000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10489000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11331000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>12315000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>13309000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>13054000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>13226000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>12793000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>12308000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>11354000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>11108000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>10207000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>9786000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>11121000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>10679000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>11201000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>11605000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>15373000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>15547000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>16826000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>16892000</v>
-      </c>
-      <c r="AJ60" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="AK60" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AL60" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18243000</v>
+      </c>
+      <c r="E61" s="3">
         <v>18400000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>18946000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>18755000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>17229000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>16953000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>16695000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>17187000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>17048000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>17241000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>15939000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>15789000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>15778000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>15746000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>14698000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>12921000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>13065000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>14108000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>14280000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>14027000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>15093000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>16200000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>16491000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>16698000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>16288000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>16313000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>15975000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>17213000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>17155000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>17160000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>19253000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>17085000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>17122000</v>
       </c>
-      <c r="AJ61" s="3">
-        <v>0</v>
-      </c>
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7586000</v>
+      </c>
+      <c r="E62" s="3">
         <v>7516000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6102000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6237000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6110000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6099000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5870000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5948000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5759000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5627000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5990000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6183000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6227000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6083000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>13327000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>15692000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>16262000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>16748000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>16745000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>17901000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>18214000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>18320000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>20866000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>20108000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>20105000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>19791000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>19776000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>18537000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>17629000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>19058000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>20646000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>16802000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>18190000</v>
-      </c>
-      <c r="AJ62" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="AK62" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AL62" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6111,8 +6260,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6218,8 +6370,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6325,115 +6480,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>44218000</v>
+      </c>
+      <c r="E66" s="3">
         <v>43017000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>41016000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>41926000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>40399000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>40204000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>39461000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>40548000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>39726000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>39900000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>38859000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>38208000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>37785000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>38601000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>39885000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>41440000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>43170000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>44455000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>44825000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>45310000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>46195000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>46434000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>49035000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>47591000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>46739000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>47780000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>46983000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>47538000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>46978000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>52771000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>51216000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>51894000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>53356000</v>
-      </c>
-      <c r="AJ66" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="AK66" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AL66" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6471,8 +6632,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6578,8 +6740,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6685,8 +6850,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6792,8 +6960,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6899,115 +7070,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>16457000</v>
+      </c>
+      <c r="E72" s="3">
         <v>15992000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>16781000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>18576000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>18766000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>20101000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>20909000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>21459000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>21739000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>21796000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>21774000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>22376000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>22570000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>22584000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>23180000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>23068000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>22827000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>21672000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>20623000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>19357000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>18200000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>16829000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>16361000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>15472000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>16017000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>16763000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>17045000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>19873000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>20110000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>29701000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>35460000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>29489000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>29536000</v>
-      </c>
-      <c r="AJ72" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="AK72" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AL72" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7113,8 +7290,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7220,8 +7400,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7327,115 +7510,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15860000</v>
+      </c>
+      <c r="E76" s="3">
         <v>15249000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16008000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>17541000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>17231000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16788000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>17355000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18311000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>18318000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>18425000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>18607000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19567000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19997000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>20181000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>20718000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>18117000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>18973000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>18880000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>18165000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>16439000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15573000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14003000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12435000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>12354000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>12537000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>12906000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>13541000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>17399000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>17911000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>26966000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>32483000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>27157000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>26865000</v>
-      </c>
-      <c r="AJ76" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="AK76" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="AL76" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7541,227 +7730,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>721000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-533000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1543000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>62000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-835000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-307000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-53000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>214000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>439000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>516000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-105000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>302000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>485000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-93000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>610000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>735000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1652000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1561000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1727000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1675000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1891000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>986000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1234000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-28000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-227000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>237000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2323000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>333000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>75000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>556000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>891000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1013000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1333000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1404000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-2527000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7799,115 +7997,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>661000</v>
+      </c>
+      <c r="E83" s="3">
         <v>638000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>608000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>665000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>605000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>639000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>506000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>576000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>568000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>567000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>494000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>585000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>599000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>664000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>654000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>668000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>684000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>752000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>655000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>725000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>745000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>717000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>726000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>724000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>700000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>724000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>713000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>739000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>646000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>840000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>407000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>836000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>829000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>837000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>228000</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8013,8 +8215,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8120,8 +8325,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8227,8 +8435,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8334,8 +8545,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8441,115 +8655,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E89" s="3">
         <v>1124000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>284000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1127000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-470000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>91000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>814000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>800000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>836000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>464000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1656000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1658000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1347000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>535000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2078000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1940000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1854000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1603000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2575000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2721000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2004000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-291000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1630000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1767000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1590000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1239000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1950000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1724000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>830000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1426000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1730000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>731000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1951000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-158000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-2717000</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8587,115 +8807,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E91" s="3">
         <v>-524000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-615000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-606000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-700000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-715000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-692000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-918000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-767000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-766000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-811000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-699000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-662000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-520000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-601000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-454000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-458000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-317000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1155000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-415000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>393000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-395000</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
       <c r="AD91" s="3">
         <v>0</v>
       </c>
       <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
         <v>433000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-442000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>1419000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-577000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-445000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-423000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-185000</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8801,8 +9025,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8908,115 +9135,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E94" s="3">
         <v>-448000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-669000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-495000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-561000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-401000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-912000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-691000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-494000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-271000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1082000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1012000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-684000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-150000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1631000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-576000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-396000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-367000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1379000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-767000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-755000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-13000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-225000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-82000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-381000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-153000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-597000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-715000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-394000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-486000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-929000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-842000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-332000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-92000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>2304000</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9054,80 +9287,81 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E96" s="3">
         <v>252000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>251000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>249000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>496000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>494000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>492000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>490000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>491000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>493000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>491000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>492000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>493000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>496000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-495000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-493000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-505000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-513000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>1561000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-518000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-522000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-521000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-2071000</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
@@ -9138,14 +9372,14 @@
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-18000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-517000</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
         <v>0</v>
       </c>
@@ -9153,16 +9387,19 @@
         <v>0</v>
       </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>1057000</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-558000</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9268,8 +9505,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9375,8 +9615,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9482,325 +9725,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E100" s="3">
         <v>-320000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-433000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1600000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1862000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-521000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-445000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-594000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-695000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>566000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-711000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-497000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1053000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-854000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1152000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1417000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2079000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1017000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1097000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2474000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1905000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-595000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-955000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-930000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1144000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>265000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1839000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-589000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1034000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-633000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1759000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1248000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1544000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-853000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1785000</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>130000</v>
+      </c>
+      <c r="E101" s="3">
         <v>123000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-181000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>87000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-15000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-54000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>85000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-32000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-57000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-41000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>24000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-99000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-117000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-45000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>24000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-99000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-117000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-45000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-42000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-45000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>36000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-48000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>103000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>70000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>20000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-86000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>27000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-64000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-20000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>30000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-40000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>9000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-168000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>100000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>283000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-802000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2238000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>961000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-708000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-724000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-398000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-368000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>705000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-52000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>117000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-447000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-510000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1623000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-152000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-738000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>174000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>57000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-565000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-620000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-947000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>553000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>825000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>85000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1265000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-459000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>356000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-584000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>303000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-678000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1427000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-336000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1003000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-2201000</v>
       </c>
     </row>
